--- a/personas_encontradas/resultado_busqueda.xlsx
+++ b/personas_encontradas/resultado_busqueda.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,28 +480,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IMG_9494.JPG</t>
+          <t>IMG_9690.JPG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9494.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9690.JPG</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0974</v>
+        <v>0.15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0974</v>
+        <v>0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0926</v>
+        <v>0.1348</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1023</v>
+        <v>0.1652</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0049</v>
+        <v>0.0152</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>84.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -523,28 +523,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IMG_9493.JPG</t>
+          <t>IMG_9692.JPG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9493.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9692.JPG</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1026</v>
+        <v>0.1647</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1026</v>
+        <v>0.1647</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0959</v>
+        <v>0.1495</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1092</v>
+        <v>0.18</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0067</v>
+        <v>0.0153</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>83.7</v>
+        <v>72.7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -566,28 +566,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IMG_9495.JPG</t>
+          <t>IMG_9635.JPG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9495.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9635.JPG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1557</v>
+        <v>0.2084</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1557</v>
+        <v>0.2084</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1499</v>
+        <v>0.1986</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1614</v>
+        <v>0.2183</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0058</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -598,39 +598,39 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>76.3</v>
+        <v>67.8</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IMG_9496.JPG</t>
+          <t>IMG_9915.JPG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9496.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9915.JPG</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2234</v>
+        <v>0.2229</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2234</v>
+        <v>0.2229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2219</v>
+        <v>0.2113</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2248</v>
+        <v>0.2345</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0015</v>
+        <v>0.0116</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>67.7</v>
+        <v>65.3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -652,28 +652,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IMG_9788.JPG</t>
+          <t>IMG_9691.JPG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9788.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9691.JPG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2224</v>
+        <v>0.1598</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2224</v>
+        <v>0.1598</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2155</v>
+        <v>0.1117</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2293</v>
+        <v>0.2078</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0069</v>
+        <v>0.0481</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>66.5</v>
+        <v>65.2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -695,28 +695,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IMG_9675.JPG</t>
+          <t>IMG_9634.JPG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9675.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9634.JPG</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2319</v>
+        <v>0.2713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2319</v>
+        <v>0.2713</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2298</v>
+        <v>0.2659</v>
       </c>
       <c r="F7" t="n">
-        <v>0.234</v>
+        <v>0.2767</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0021</v>
+        <v>0.0054</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>66.3</v>
+        <v>59.9</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -738,28 +738,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IMG_9673.JPG</t>
+          <t>IMG_9914.JPG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9673.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9914.JPG</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.2295</v>
+        <v>0.258</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2295</v>
+        <v>0.258</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2221</v>
+        <v>0.2401</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2368</v>
+        <v>0.2759</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0073</v>
+        <v>0.0179</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>65.40000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -781,28 +781,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IMG_9786.JPG</t>
+          <t>IMG_9919.JPG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9786.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9919.JPG</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.2361</v>
+        <v>0.2612</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2361</v>
+        <v>0.2612</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2313</v>
+        <v>0.2334</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2409</v>
+        <v>0.2891</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0048</v>
+        <v>0.0278</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -813,310 +813,9 @@
         <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>65.09999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="K9" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IMG_9874.JPG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9874.JPG</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.2409</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2409</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.2379</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.2439</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>100</v>
-      </c>
-      <c r="J10" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IMG_9789.JPG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9789.JPG</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.2427</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.2427</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.2464</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>100</v>
-      </c>
-      <c r="J11" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IMG_9674.JPG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9674.JPG</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.2467</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>100</v>
-      </c>
-      <c r="J12" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>IMG_9787.JPG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9787.JPG</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.2596</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.2596</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.2564</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.2627</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>100</v>
-      </c>
-      <c r="J13" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IMG_9790.JPG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9790.JPG</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.2825</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.2889</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>100</v>
-      </c>
-      <c r="J14" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IMG_9791.JPG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9791.JPG</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.2936</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.2936</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.2934</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.2939</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>100</v>
-      </c>
-      <c r="J15" t="n">
-        <v>58</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>IMG_9647.JPG</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9647.JPG</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.2871</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.2871</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.2792</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>100</v>
-      </c>
-      <c r="J16" t="n">
-        <v>57</v>
-      </c>
-      <c r="K16" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -1201,28 +900,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IMG_9873.JPG</t>
+          <t>IMG_9604.JPG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9873.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9604.JPG</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3209</v>
+        <v>0.2971</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3209</v>
+        <v>0.2971</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3187</v>
+        <v>0.2807</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3232</v>
+        <v>0.3135</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0022</v>
+        <v>0.0164</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1233,7 +932,7 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1249,28 +948,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IMG_9872.JPG</t>
+          <t>IMG_9918.JPG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9872.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9918.JPG</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3272</v>
+        <v>0.2856</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3272</v>
+        <v>0.2856</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3271</v>
+        <v>0.2546</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3272</v>
+        <v>0.3166</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0001</v>
+        <v>0.031</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1281,7 +980,7 @@
         <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>53.2</v>
+        <v>51.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1297,28 +996,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IMG_9792.JPG</t>
+          <t>IMG_9641.JPG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9792.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9641.JPG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3244</v>
+        <v>0.3148</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3244</v>
+        <v>0.3148</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3207</v>
+        <v>0.2974</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3282</v>
+        <v>0.3322</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0038</v>
+        <v>0.0174</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1329,7 +1028,7 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>52.7</v>
+        <v>50.7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1345,28 +1044,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IMG_20260409_112939.jpg</t>
+          <t>IMG_9786.JPG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_20260409_112939.jpg</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9786.JPG</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3353</v>
+        <v>0.329</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3353</v>
+        <v>0.329</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3327</v>
+        <v>0.3096</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3379</v>
+        <v>0.3483</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0026</v>
+        <v>0.0194</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1377,7 +1076,7 @@
         <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>51.5</v>
+        <v>48.2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1393,28 +1092,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IMG_20260409_112937.jpg</t>
+          <t>IMG_9759.JPG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_20260409_112937.jpg</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9759.JPG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3501</v>
+        <v>0.3419</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3501</v>
+        <v>0.3419</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3477</v>
+        <v>0.3283</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3525</v>
+        <v>0.3555</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0024</v>
+        <v>0.0136</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1425,7 +1124,7 @@
         <v>50</v>
       </c>
       <c r="J6" t="n">
-        <v>34.4</v>
+        <v>32.8</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1434,35 +1133,35 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>votacion</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IMG_9595.JPG</t>
+          <t>IMG_9588.JPG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9595.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9588.JPG</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3412</v>
+        <v>0.3309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3412</v>
+        <v>0.3309</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3323</v>
+        <v>0.3095</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3502</v>
+        <v>0.3522</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0214</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1473,7 +1172,7 @@
         <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>34</v>
+        <v>32.4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1489,28 +1188,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IMG_9754.JPG</t>
+          <t>IMG_20260409_112531.jpg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9754.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_20260409_112531.jpg</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.3494</v>
+        <v>0.3728</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3494</v>
+        <v>0.3728</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3418</v>
+        <v>0.3496</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3571</v>
+        <v>0.3961</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0076</v>
+        <v>0.0232</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1521,7 +1220,7 @@
         <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>33.2</v>
+        <v>29.2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1530,7 +1229,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>votacion</t>
+          <t>distancia</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1578,19 +1277,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IMG_9494.JPG</t>
+          <t>IMG_9690.JPG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9494.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9690.JPG</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0974</v>
+        <v>0.15</v>
       </c>
       <c r="D2" t="n">
-        <v>84.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1601,19 +1300,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IMG_9493.JPG</t>
+          <t>IMG_9692.JPG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9493.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9692.JPG</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1026</v>
+        <v>0.1647</v>
       </c>
       <c r="D3" t="n">
-        <v>83.7</v>
+        <v>72.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1624,42 +1323,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IMG_9495.JPG</t>
+          <t>IMG_9635.JPG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9495.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9635.JPG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1557</v>
+        <v>0.2084</v>
       </c>
       <c r="D4" t="n">
-        <v>76.3</v>
+        <v>67.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IMG_9496.JPG</t>
+          <t>IMG_9915.JPG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9496.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9915.JPG</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2234</v>
+        <v>0.2229</v>
       </c>
       <c r="D5" t="n">
-        <v>67.7</v>
+        <v>65.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1670,19 +1369,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IMG_9788.JPG</t>
+          <t>IMG_9691.JPG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9788.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9691.JPG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2224</v>
+        <v>0.1598</v>
       </c>
       <c r="D6" t="n">
-        <v>66.5</v>
+        <v>65.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1693,19 +1392,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IMG_9675.JPG</t>
+          <t>IMG_9634.JPG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9675.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9634.JPG</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2319</v>
+        <v>0.2713</v>
       </c>
       <c r="D7" t="n">
-        <v>66.3</v>
+        <v>59.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1716,19 +1415,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IMG_9673.JPG</t>
+          <t>IMG_9914.JPG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9673.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9914.JPG</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.2295</v>
+        <v>0.258</v>
       </c>
       <c r="D8" t="n">
-        <v>65.40000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1739,182 +1438,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IMG_9786.JPG</t>
+          <t>IMG_9919.JPG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9786.JPG</t>
+          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9919.JPG</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.2361</v>
+        <v>0.2612</v>
       </c>
       <c r="D9" t="n">
-        <v>65.09999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IMG_9874.JPG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9874.JPG</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.2409</v>
-      </c>
-      <c r="D10" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IMG_9789.JPG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9789.JPG</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.2427</v>
-      </c>
-      <c r="D11" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IMG_9674.JPG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9674.JPG</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.2408</v>
-      </c>
-      <c r="D12" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>IMG_9787.JPG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9787.JPG</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.2596</v>
-      </c>
-      <c r="D13" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IMG_9790.JPG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9790.JPG</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="D14" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IMG_9791.JPG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9791.JPG</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.2936</v>
-      </c>
-      <c r="D15" t="n">
-        <v>58</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>IMG_9647.JPG</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>fotos_prueba/Fotos SJB 09-04-2026/IMG_9647.JPG</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.2871</v>
-      </c>
-      <c r="D16" t="n">
-        <v>57</v>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
@@ -1947,7 +1485,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Aparece graduando_3</t>
+          <t>Aparece Miguel Peñaloza</t>
         </is>
       </c>
     </row>
@@ -3205,7 +2743,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -3222,7 +2760,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -3239,7 +2777,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -3256,7 +2794,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5123,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5140,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5327,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -6231,7 +5769,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -6248,7 +5786,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -6265,7 +5803,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6058,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6075,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6092,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -8135,7 +7673,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -8152,7 +7690,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -8169,7 +7707,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -8186,7 +7724,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -8203,7 +7741,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -8220,7 +7758,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9152,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -10294,7 +9832,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -10311,7 +9849,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -10379,7 +9917,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
     </row>
